--- a/data/rules/phase1_complex_rules.xlsx
+++ b/data/rules/phase1_complex_rules.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -468,47 +468,92 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rule coverage:</t>
+          <t>Scope: every rule's Target Table must exist in the env's target schema.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BR-AGG-*        aggregation on the final table via inner select</t>
+          <t>This workbook targets stage-schema objects (cup00301, cup01201,</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BR-FK-*/BR-SCOPED-*  correlated EXISTS / Where-Clause subqueries</t>
+          <t>v_dim_customer_src) — run it ONLY with the hop-1 env above. On a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BR-TAXID-*      conditional business predicate (S-type tax ids are 9 digits)</t>
+          <t>mismatched env (e.g. hop 3) the suite skips with the missing-table</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BR-JOIN-*       multi-file auto-join recomputed vs the DB join view</t>
+          <t>reason instead of reporting a wall of UndefinedTable errors; a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>partial match still lets the genuinely broken rule ERROR loudly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rule coverage:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BR-AGG-*        aggregation on the final table via inner select</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BR-FK-*/BR-SCOPED-*  correlated EXISTS / Where-Clause subqueries</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BR-TAXID-*      conditional business predicate (S-type tax ids are 9 digits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BR-JOIN-*       multi-file auto-join recomputed vs the DB join view</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">  BR-LOOKUP-*/BR-DEFAULT-*  differing-key join + null-default logic</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">  BR-EXTRACT-*    cross-file watermark consistency</t>
         </is>

--- a/data/rules/phase1_complex_rules.xlsx
+++ b/data/rules/phase1_complex_rules.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,6 +634,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -680,6 +685,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Customer number must be unique across the landed customer table</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -726,6 +736,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No bank may carry more than 80 customer rows in the landed customer table</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -772,6 +787,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Every legal-entity row must reference a customer number that exists in the customer table</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -818,6 +838,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Tax ids marked as S-type (Social Security) must be exactly nine digits</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -868,6 +893,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>The legal entity in the customer join view must equal the value recomputed by joining the customer and legal-entity files on customer number</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -922,6 +952,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Each customer with a tax-id type gets its description from the reference-data lookup</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -972,6 +1007,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>When a tax-id type has no reference description it defaults to 'SOCIAL SECURITY NUMBER'</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1024,6 +1064,11 @@
       <c r="L9" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Customer and legal-entity extracts must carry the same load date for each customer number</t>
         </is>
       </c>
     </row>
@@ -1072,6 +1117,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>State code must be exactly two uppercase letters</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1118,6 +1168,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Job/birth date must be a valid date in YYYYMMDD format</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1162,6 +1217,11 @@
       <c r="L12" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Legal entity must be populated for every legal-entity row whose customer exists in the customer file</t>
         </is>
       </c>
     </row>
